--- a/athena/Validación Athena.xlsx
+++ b/athena/Validación Athena.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TFM\TFM-segmentacion-inmobiliaria\athena\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459E211E-980C-404E-8C04-90B4247A2E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F7570D-D698-4468-B23F-4DFCAC6189A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>Dataset</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>integrado_join_municipal</t>
-  </si>
-  <si>
-    <t>REVISAR</t>
   </si>
 </sst>
 </file>
@@ -868,9 +865,6 @@
       <c r="E20" s="1">
         <v>0</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>38</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
